--- a/260628.xlsx
+++ b/260628.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tac3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3431D4DA-2421-437A-A389-09DC437F4F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6A365F-EBA6-40A9-8359-D9FA4DB3941B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8890" yWindow="2290" windowWidth="16180" windowHeight="11170" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9260" yWindow="4110" windowWidth="16150" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -29,18 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t xml:space="preserve">Und die Vorgaben des Bundesverfassungsgerichtes sind auch für mich Richtschnur.
-Geuther: Was die Gewalttaten in Deutschland betrifft, beim Angriff in einem Zug bei Würzburg hat Bundesinnenminister Thomas de Maizière von einer Tat gesprochen, die vielleicht im Grenzbereich von Terrorismus und Amoklauf liege.
-Beim Täter von Ansbach ist die Frage, ob er von einer weiteren Person im Internet angeleitet oder aufgestachelt, nämlich der Messerangriff einer 15-Jährigen auf einen Bundespolizisten mit möglichen Verbindungen zum sogenannten IS im Februar.
-Das heißt, die Ränder der terroristischen Situation verschwimmen sozusagen.
-Stellt Sie das vor rechtliche Probleme?
-Frank: Nein.
-Die drei von Ihnen genannten Taten lassen sich mit dem rechtlichen Instrumentarium, das uns zur Verfügung steht, sehr gut lösen.
-Der Angriff auf die Passanten im Regionalzug nach Würzburg </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t xml:space="preserve">Detjen: Im Zusammenhang mit dem Thema Referendum ist das Stichwort Brexit eben schon.
 Was erwarten Sie, was erwartet Hamburg von den jetzt oder Anfang nächsten Jahres, wann auch immer beginnenden Austrittsverhandlungen mit Großbritannien?
@@ -76,6 +65,15 @@
 Mattes: Auch das nicht.
 Wir arbeiten als Konzern weltweit sehr, sehr eng vernetzt zusammen</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sind auch für mich Richtschnur.</t>
+  </si>
+  <si>
+    <t>aufgestachelt</t>
+  </si>
+  <si>
+    <t>Regionalzug</t>
   </si>
 </sst>
 </file>
@@ -403,10 +401,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D344D2-CBF1-4C07-8FA6-974A8E05E08E}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CF02851-22FD-43A1-B6AB-F49DC5B190B6}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.33203125" customWidth="1"/>
+    <col min="1" max="1" width="26.4140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
@@ -420,12 +447,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CF02851-22FD-43A1-B6AB-F49DC5B190B6}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29400EC7-2845-4E26-B40A-2BD8512EAFB6}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.4140625" customWidth="1"/>
+    <col min="1" max="1" width="30.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
@@ -439,25 +466,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29400EC7-2845-4E26-B40A-2BD8512EAFB6}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="30.58203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D71DE68B-0A14-4672-9946-137C75643FE0}">
   <dimension ref="A1"/>
@@ -468,7 +476,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="238" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/260628.xlsx
+++ b/260628.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6A365F-EBA6-40A9-8359-D9FA4DB3941B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6712E7A2-82A0-4089-8094-609731157A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9260" yWindow="4110" windowWidth="16150" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="16150" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -70,10 +70,11 @@
     <t>sind auch für mich Richtschnur.</t>
   </si>
   <si>
-    <t>aufgestachelt</t>
+    <t>Regionalzug</t>
   </si>
   <si>
-    <t>Regionalzug</t>
+    <t>aufgestachelt 煽动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -414,12 +415,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/260628.xlsx
+++ b/260628.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6712E7A2-82A0-4089-8094-609731157A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{658FA0D5-852D-4524-BAA9-3122A59FE0ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="16150" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="460" yWindow="4110" windowWidth="23470" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -29,21 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t xml:space="preserve">Detjen: Im Zusammenhang mit dem Thema Referendum ist das Stichwort Brexit eben schon.
-Was erwarten Sie, was erwartet Hamburg von den jetzt oder Anfang nächsten Jahres, wann auch immer beginnenden Austrittsverhandlungen mit Großbritannien?
-Welche.
-Handelsbeziehungen in ganz früher Zeit zum englischen Königsreich gegeben.
-Und ich glaube, man darf sich nichts vormachen, es wird auch zu einem Austrittsantrag kommen.
-Für mich ist das natürlich Anlass zu hoffen, dass dann Bedingungen miteinander vereinbart werden, die eine gute wirtschaftliche Zusammenarbeit auch in Zukunft möglich machen.
-Und ich glaube, es gibt ja auch gute Beispiele, wie das geschieht mit Norwegen oder der Schweiz zum Beispiel.
-Detjen: Sie haben jetzt die Bedeutung des Handels angesprochen.
-Damit kommen wir schon fast automatisch zu einem anderen Thema, das Ihre Partei beschäftigt,  mit Kanada, stehen zur Debatte.
-Die SPD will sich am 19.
-September auf einem Parteikonvent in Wolfsburg </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>unter Generalverdacht zu stellen, da bin ich sehr froh darüber, dass auch der CDU-Bundesinnenminister das nicht mitmachen will.
 Diese scharfmacherischen Vorschläge aus den Reihen der CDU und der CSU gehen ja eher ein bisschen zurück in die unseligen Zeiten, in denen ein CDU-Ministerpräsident in Hessen, Herr Koch, einen ausländerfeindlichen Wahlkampf gemacht hat.
@@ -75,6 +61,16 @@
   <si>
     <t>aufgestachelt 煽动</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stichwort</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> man darf sich nichts vormachen,  einem Austrittsantrag natürlich Anlass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>geschieht</t>
   </si>
 </sst>
 </file>
@@ -410,17 +406,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -431,15 +427,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CF02851-22FD-43A1-B6AB-F49DC5B190B6}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -458,7 +464,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -477,7 +483,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="238" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
